--- a/payroll/2026/excel/20260928-0929.xlsx
+++ b/payroll/2026/excel/20260928-0929.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848B25F7-25EF-476E-A865-8523B23AE142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1912EB-CE1D-4FE7-A74C-DFADF58BBB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>人员</t>
   </si>
@@ -447,10 +447,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -471,11 +468,74 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -839,140 +899,140 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="70.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="66.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.625" style="6"/>
+    <col min="1" max="1" width="25.875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="66.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>592</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>528</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>864</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>1952</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>SUM(D3:D6)</f>
         <v>3936</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -985,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76FA64F-2994-4A17-8B67-4FDBD51AF35E}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="21.75" defaultRowHeight="57.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" customWidth="1"/>
@@ -997,38 +1057,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1036,24 +1096,24 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <f>E3+F3+G3+H3</f>
         <v>267</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8">
         <v>39</v>
       </c>
-      <c r="F3" s="9">
-        <v>35</v>
-      </c>
-      <c r="G3" s="9">
-        <v>54</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="F3" s="8">
+        <v>35</v>
+      </c>
+      <c r="G3" s="8">
+        <v>54</v>
+      </c>
+      <c r="H3" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1061,45 +1121,45 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="9">
-        <f t="shared" ref="C4:C29" si="0">E4+F4+G4+H4</f>
+      <c r="C4" s="8">
+        <f t="shared" ref="C4:C28" si="0">E4+F4+G4+H4</f>
         <v>93</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8">
         <v>39</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9">
-        <v>54</v>
-      </c>
-      <c r="H4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8">
+        <v>54</v>
+      </c>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8">
         <v>39</v>
       </c>
-      <c r="F5" s="9">
-        <v>35</v>
-      </c>
-      <c r="G5" s="9">
-        <v>54</v>
-      </c>
-      <c r="H5" s="9">
+      <c r="F5" s="8">
+        <v>35</v>
+      </c>
+      <c r="G5" s="8">
+        <v>54</v>
+      </c>
+      <c r="H5" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1107,87 +1167,89 @@
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
         <v>39</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9">
-        <v>54</v>
-      </c>
-      <c r="H6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8">
+        <v>54</v>
+      </c>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="9">
-        <f t="shared" si="0"/>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
         <v>39</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9">
-        <v>39</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="F7" s="8">
+        <v>35</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>39</v>
       </c>
-      <c r="F8" s="9">
-        <v>35</v>
-      </c>
-      <c r="G8" s="9">
-        <v>54</v>
-      </c>
-      <c r="H8" s="9"/>
+      <c r="F8" s="8">
+        <v>35</v>
+      </c>
+      <c r="G8" s="8">
+        <v>54</v>
+      </c>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
         <v>39</v>
       </c>
-      <c r="F9" s="9">
-        <v>35</v>
-      </c>
-      <c r="G9" s="9">
-        <v>54</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="F9" s="8">
+        <v>35</v>
+      </c>
+      <c r="G9" s="8">
+        <v>54</v>
+      </c>
+      <c r="H9" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1195,41 +1257,41 @@
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>39</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9">
-        <v>54</v>
-      </c>
-      <c r="H10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8">
+        <v>54</v>
+      </c>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <f t="shared" si="0"/>
         <v>178</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8">
         <v>39</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9">
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1237,22 +1299,22 @@
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>39</v>
       </c>
-      <c r="F12" s="9">
-        <v>35</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9">
+      <c r="F12" s="8">
+        <v>35</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1260,22 +1322,22 @@
       <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <f t="shared" si="0"/>
         <v>232</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8">
         <v>39</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
-        <v>54</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8">
+        <v>54</v>
+      </c>
+      <c r="H13" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1283,24 +1345,24 @@
       <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8">
         <v>39</v>
       </c>
-      <c r="F14" s="9">
-        <v>35</v>
-      </c>
-      <c r="G14" s="9">
-        <v>54</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="F14" s="8">
+        <v>35</v>
+      </c>
+      <c r="G14" s="8">
+        <v>54</v>
+      </c>
+      <c r="H14" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1308,43 +1370,43 @@
       <c r="A15" s="3">
         <v>13</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
         <v>39</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8">
         <v>39</v>
       </c>
-      <c r="F16" s="9">
-        <v>35</v>
-      </c>
-      <c r="G16" s="9">
-        <v>54</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="F16" s="8">
+        <v>35</v>
+      </c>
+      <c r="G16" s="8">
+        <v>54</v>
+      </c>
+      <c r="H16" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1352,24 +1414,24 @@
       <c r="A17" s="3">
         <v>15</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8">
         <v>39</v>
       </c>
-      <c r="F17" s="9">
-        <v>35</v>
-      </c>
-      <c r="G17" s="9">
-        <v>54</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="F17" s="8">
+        <v>35</v>
+      </c>
+      <c r="G17" s="8">
+        <v>54</v>
+      </c>
+      <c r="H17" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1377,22 +1439,22 @@
       <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <f t="shared" si="0"/>
         <v>228</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9">
-        <v>35</v>
-      </c>
-      <c r="G18" s="9">
-        <v>54</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8">
+        <v>35</v>
+      </c>
+      <c r="G18" s="8">
+        <v>54</v>
+      </c>
+      <c r="H18" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1400,58 +1462,58 @@
       <c r="A19" s="3">
         <v>17</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="9">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9">
-        <v>35</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="C19" s="8">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8">
+        <v>35</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9">
-        <v>35</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="C20" s="8">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8">
+        <v>35</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9">
-        <v>35</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8">
+        <v>35</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1459,20 +1521,20 @@
       <c r="A22" s="3">
         <v>20</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9">
-        <v>35</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8">
+        <v>35</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8">
         <v>139</v>
       </c>
     </row>
@@ -1480,143 +1542,124 @@
       <c r="A23" s="3">
         <v>21</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="9">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9">
-        <v>35</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
+      <c r="B23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="8">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
+        <v>35</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="9">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9">
-        <v>35</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
+      <c r="B24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="8">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8">
+        <v>54</v>
+      </c>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="9">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9">
-        <v>54</v>
-      </c>
-      <c r="H25" s="9"/>
+      <c r="B25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="8">
+        <f t="shared" si="0"/>
+        <v>193</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8">
+        <v>54</v>
+      </c>
+      <c r="H25" s="8">
+        <v>139</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="9">
-        <f t="shared" si="0"/>
-        <v>193</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9">
-        <v>54</v>
-      </c>
-      <c r="H26" s="9">
-        <v>139</v>
-      </c>
+      <c r="B26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="8">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8">
+        <v>54</v>
+      </c>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="9">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9">
-        <v>54</v>
-      </c>
-      <c r="H27" s="9"/>
+      <c r="B27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="8">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8">
+        <v>54</v>
+      </c>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="9">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9">
-        <v>54</v>
-      </c>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>27</v>
-      </c>
-      <c r="B29" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C28" s="8">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9">
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8">
         <v>139</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
+    <row r="29" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="1">
-        <f>SUM(C3:C29)</f>
+      <c r="C29" s="1">
+        <f>SUM(C3:C28)</f>
         <v>3920</v>
       </c>
     </row>
@@ -1625,14 +1668,17 @@
     <mergeCell ref="B1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1 B30:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <conditionalFormatting sqref="B29:B1048576 B1">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="B29:B1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/payroll/2026/excel/20260928-0929.xlsx
+++ b/payroll/2026/excel/20260928-0929.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1912EB-CE1D-4FE7-A74C-DFADF58BBB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF54B70-10B5-4F1E-91B6-CDA31638D8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
@@ -202,6 +202,23 @@
   </si>
   <si>
     <t>情有毒钟</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0928-0929 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集体产出</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -281,24 +298,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> ( 3,769 + 353 = 4122 )</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">0928-0929 </t>
+      <t xml:space="preserve"> ( 3,769 + 353 -300(</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
+        <sz val="14"/>
+        <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>集体产出</t>
+      <t>大虾天玄项链</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>300) = 3822 )</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -475,57 +494,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -910,7 +879,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1058,13 +1027,14 @@
   <sheetData>
     <row r="1" spans="1:8" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1665,20 +1635,20 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B29:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
